--- a/data/trans_orig/P36BPD12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen frutos secos a la semana en 2023</t>
+          <t>Población según el número de veces que consumen frutos secos a la semana en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137224</t>
+          <t>139802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181692</t>
+          <t>182955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145517</t>
+          <t>146201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181842</t>
+          <t>181366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>296950</t>
+          <t>297301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354340</t>
+          <t>351783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213230</t>
+          <t>211869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258338</t>
+          <t>257214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161944</t>
+          <t>160599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196289</t>
+          <t>195735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>386388</t>
+          <t>384725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>443832</t>
+          <t>442584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93902</t>
+          <t>90629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131338</t>
+          <t>127804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122411</t>
+          <t>121780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>190405</t>
+          <t>190513</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241054</t>
+          <t>239609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135272</t>
+          <t>135708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177358</t>
+          <t>178015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134071</t>
+          <t>131666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165602</t>
+          <t>166164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278196</t>
+          <t>278661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>334196</t>
+          <t>333375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186414</t>
+          <t>185677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231242</t>
+          <t>229056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129424</t>
+          <t>128422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161494</t>
+          <t>160504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>323304</t>
+          <t>327276</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>383277</t>
+          <t>382216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69578</t>
+          <t>69570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103630</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75492</t>
+          <t>74355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103755</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152433</t>
+          <t>151241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195738</t>
+          <t>198239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54641</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231139</t>
+          <t>235590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>89138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284387</t>
+          <t>282156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291363</t>
+          <t>287022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>579967</t>
+          <t>574778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>70705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90348</t>
+          <t>90644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371108</t>
+          <t>371260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>699561</t>
+          <t>690848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>154339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44307</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>54095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188368</t>
+          <t>189040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>326066</t>
+          <t>325459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>395885</t>
+          <t>398208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142379</t>
+          <t>146203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>351256</t>
+          <t>349868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436295</t>
+          <t>441074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712916</t>
+          <t>718896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424882</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495350</t>
+          <t>498603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428593</t>
+          <t>428833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>739768</t>
+          <t>750579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>886895</t>
+          <t>883429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1316550</t>
+          <t>1310572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182309</t>
+          <t>182342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>243543</t>
+          <t>240396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85535</t>
+          <t>78341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206045</t>
+          <t>206148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>254073</t>
+          <t>271514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>424495</t>
+          <t>426025</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139958</t>
+          <t>140604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182372</t>
+          <t>182045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207828</t>
+          <t>211616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325309</t>
+          <t>325242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>364845</t>
+          <t>360896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>488975</t>
+          <t>487341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182154</t>
+          <t>182709</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>229064</t>
+          <t>227884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>248182</t>
+          <t>253385</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383982</t>
+          <t>382328</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>453909</t>
+          <t>446693</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>594557</t>
+          <t>593566</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>85875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132479</t>
+          <t>130812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138340</t>
+          <t>136133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>396205</t>
+          <t>367971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245383</t>
+          <t>243677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>505365</t>
+          <t>482662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>308235</t>
+          <t>307865</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>361523</t>
+          <t>359640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>352232</t>
+          <t>351647</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>419896</t>
+          <t>420386</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93516</t>
+          <t>92755</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>144897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>287799</t>
+          <t>288073</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>338847</t>
+          <t>339584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>470451</t>
+          <t>468534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43031</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92385</t>
+          <t>95587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97759</t>
+          <t>98893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>138657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153370</t>
+          <t>157174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>221061</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>798805</t>
+          <t>735685</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1136223</t>
+          <t>1133303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1020132</t>
+          <t>1022845</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1367186</t>
+          <t>1360267</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1967018</t>
+          <t>1942502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2449431</t>
+          <t>2445944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1505910</t>
+          <t>1509760</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2043847</t>
+          <t>2150733</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1455269</t>
+          <t>1451919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1955611</t>
+          <t>1968027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3011523</t>
+          <t>3015483</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3824965</t>
+          <t>3769778</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>537870</t>
+          <t>505762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>751433</t>
+          <t>749806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>603581</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>932823</t>
+          <t>905577</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1211343</t>
+          <t>1218850</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1585753</t>
+          <t>1591744</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>159925</t>
+          <t>168475</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139802</t>
+          <t>145517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182955</t>
+          <t>190422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>163064</t>
+          <t>173262</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146201</t>
+          <t>155874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181366</t>
+          <t>191272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>322989</t>
+          <t>341738</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297301</t>
+          <t>311646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>351783</t>
+          <t>370141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>235038</t>
+          <t>253004</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211869</t>
+          <t>227657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257214</t>
+          <t>275243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>178682</t>
+          <t>197484</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160599</t>
+          <t>180341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195735</t>
+          <t>216494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>413720</t>
+          <t>450488</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384725</t>
+          <t>420377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442584</t>
+          <t>480708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90629</t>
+          <t>110766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127804</t>
+          <t>151957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105721</t>
+          <t>117665</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90474</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121780</t>
+          <t>135643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>215344</t>
+          <t>246191</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>220630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239609</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504585</t>
+          <t>550006</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504585</t>
+          <t>550006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504585</t>
+          <t>550006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952052</t>
+          <t>1038417</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952052</t>
+          <t>1038417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952052</t>
+          <t>1038417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>156936</t>
+          <t>162163</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135708</t>
+          <t>139190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178015</t>
+          <t>185139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>149524</t>
+          <t>161240</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131666</t>
+          <t>142826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>166164</t>
+          <t>178784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>306460</t>
+          <t>323403</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278661</t>
+          <t>297374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333375</t>
+          <t>349712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>207740</t>
+          <t>225262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185677</t>
+          <t>202596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229056</t>
+          <t>248827</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>144154</t>
+          <t>161646</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128422</t>
+          <t>143842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160504</t>
+          <t>178702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>351894</t>
+          <t>386908</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>327276</t>
+          <t>357815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>382216</t>
+          <t>418351</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>93514</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>74091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103771</t>
+          <t>113057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>99519</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74355</t>
+          <t>83695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>115694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>173439</t>
+          <t>193033</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151241</t>
+          <t>169517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198239</t>
+          <t>218175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>449932</t>
+          <t>480939</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449932</t>
+          <t>480939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449932</t>
+          <t>480939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>831793</t>
+          <t>903344</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>831793</t>
+          <t>903344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831793</t>
+          <t>903344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141527</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56302</t>
+          <t>133113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235590</t>
+          <t>176596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43148</t>
+          <t>47330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>68478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>193566</t>
+          <t>212348</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89138</t>
+          <t>188029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282156</t>
+          <t>234699</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>434013</t>
+          <t>213284</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>287022</t>
+          <t>191968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>574778</t>
+          <t>236702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>90812</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70705</t>
+          <t>79531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90644</t>
+          <t>102224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>514017</t>
+          <t>304097</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371260</t>
+          <t>279725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>690848</t>
+          <t>329512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>85812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154339</t>
+          <t>124204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>126918</t>
+          <t>141920</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54095</t>
+          <t>122360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189040</t>
+          <t>163707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667590</t>
+          <t>470868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667590</t>
+          <t>470868</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667590</t>
+          <t>470868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834501</t>
+          <t>658365</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834501</t>
+          <t>658365</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834501</t>
+          <t>658365</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>358667</t>
+          <t>388467</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>325459</t>
+          <t>354937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>398208</t>
+          <t>425740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>271555</t>
+          <t>296694</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>271185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>349868</t>
+          <t>319221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>630222</t>
+          <t>685161</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>441074</t>
+          <t>642985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>718896</t>
+          <t>728391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>462316</t>
+          <t>508777</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429223</t>
+          <t>474037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498603</t>
+          <t>544871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>549780</t>
+          <t>386786</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428833</t>
+          <t>359358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>750579</t>
+          <t>412934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1012096</t>
+          <t>895563</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>883429</t>
+          <t>849332</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310572</t>
+          <t>938350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>212294</t>
+          <t>232951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182342</t>
+          <t>204021</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240396</t>
+          <t>264981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>156212</t>
+          <t>177172</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78341</t>
+          <t>155881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206148</t>
+          <t>199462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>368506</t>
+          <t>410123</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271514</t>
+          <t>374526</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>426025</t>
+          <t>449688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033277</t>
+          <t>1130194</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033277</t>
+          <t>1130194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033277</t>
+          <t>1130194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977547</t>
+          <t>860652</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977547</t>
+          <t>860652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977547</t>
+          <t>860652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990846</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010824</t>
+          <t>1990846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>160527</t>
+          <t>179990</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140604</t>
+          <t>157874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182045</t>
+          <t>203243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>317746</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211616</t>
+          <t>295661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325242</t>
+          <t>342113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>445220</t>
+          <t>497736</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>360896</t>
+          <t>461387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487341</t>
+          <t>530832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>204351</t>
+          <t>252875</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>226887</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>227884</t>
+          <t>277920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>336215</t>
+          <t>380864</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>253385</t>
+          <t>356914</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>382328</t>
+          <t>403387</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>540566</t>
+          <t>633739</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>446693</t>
+          <t>599909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>593566</t>
+          <t>669498</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108535</t>
+          <t>133454</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85875</t>
+          <t>111599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130812</t>
+          <t>160196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>217091</t>
+          <t>128847</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136133</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>367971</t>
+          <t>146442</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>325626</t>
+          <t>262301</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>243677</t>
+          <t>234538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>482662</t>
+          <t>296892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473413</t>
+          <t>566319</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473413</t>
+          <t>566319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473413</t>
+          <t>566319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>837999</t>
+          <t>827457</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>837999</t>
+          <t>827457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>837999</t>
+          <t>827457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1311412</t>
+          <t>1393776</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1311412</t>
+          <t>1393776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1311412</t>
+          <t>1393776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>75685</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>332097</t>
+          <t>362026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307865</t>
+          <t>333970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>359640</t>
+          <t>390262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>386203</t>
+          <t>416096</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>351647</t>
+          <t>380829</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>420386</t>
+          <t>452018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>119193</t>
+          <t>116653</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92755</t>
+          <t>93361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144897</t>
+          <t>140158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>312748</t>
+          <t>345126</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>288073</t>
+          <t>316897</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>339584</t>
+          <t>374671</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>431941</t>
+          <t>461779</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>395617</t>
+          <t>424944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>468534</t>
+          <t>499319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>66505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95587</t>
+          <t>91429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>116526</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98893</t>
+          <t>117127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138657</t>
+          <t>162144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,27 +3301,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>183733</t>
+          <t>203634</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>157174</t>
+          <t>171811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>236565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1031688</t>
+          <t>1108246</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>735685</t>
+          <t>1045345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1133303</t>
+          <t>1166750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1252972</t>
+          <t>1368235</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1022845</t>
+          <t>1315004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1360267</t>
+          <t>1420001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2284660</t>
+          <t>2476481</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1942502</t>
+          <t>2396315</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2445944</t>
+          <t>2550507</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1662651</t>
+          <t>1569855</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1509760</t>
+          <t>1504222</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2150733</t>
+          <t>1635228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1601583</t>
+          <t>1562719</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1451919</t>
+          <t>1512936</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1968027</t>
+          <t>1621502</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3264234</t>
+          <t>3132574</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3015483</t>
+          <t>3049262</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3769778</t>
+          <t>3211947</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>674965</t>
+          <t>757452</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>505762</t>
+          <t>707559</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>749806</t>
+          <t>821725</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>718601</t>
+          <t>699749</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>603581</t>
+          <t>655683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>905577</t>
+          <t>738646</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1393566</t>
+          <t>1457201</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1218850</t>
+          <t>1391305</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1591744</t>
+          <t>1533983</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3369305</t>
+          <t>3435553</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3369305</t>
+          <t>3435553</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3369305</t>
+          <t>3435553</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3573155</t>
+          <t>3630703</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3573155</t>
+          <t>3630703</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3573155</t>
+          <t>3630703</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6942460</t>
+          <t>7066256</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6942460</t>
+          <t>7066256</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6942460</t>
+          <t>7066256</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
